--- a/examples/extensions/thai_bim/examples/stair-Spiral-BBS.xlsx
+++ b/examples/extensions/thai_bim/examples/stair-Spiral-BBS.xlsx
@@ -228,7 +228,7 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O2" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -440,7 +440,7 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O7" s="0" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="N11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O11" s="0" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="N12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O12" s="0" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="N13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O13" s="0" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="N14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="O14" s="0" t="inlineStr">
@@ -1646,12 +1646,12 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">dfb97f2cfecb4cfc</t>
+          <t xml:space="preserve">28660532f64243ac</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -1719,12 +1719,12 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc4541b249bc4833</t>
+          <t xml:space="preserve">af10989e6cd14cba</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">56c1bfef25b84e2a</t>
+          <t xml:space="preserve">5c3553e6b78a4b13</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1865,12 +1865,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">95447c7180ba4453</t>
+          <t xml:space="preserve">ed82e35948eb471e</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -1938,12 +1938,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6432aa1cf0504982</t>
+          <t xml:space="preserve">8b04a70d42e3415c</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">20f255eda0f14db9</t>
+          <t xml:space="preserve">317de41f5fd44d5b</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -2084,12 +2084,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2cd0cc2814d04a05</t>
+          <t xml:space="preserve">508d10a9e1e44aab</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -2157,12 +2157,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">55590b10a10040eb</t>
+          <t xml:space="preserve">529ccdfbc6a549ac</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -2230,12 +2230,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b247c2a338214de4</t>
+          <t xml:space="preserve">677b5b31e4a84fc9</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -2303,12 +2303,12 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">51be4ee3b17646a5</t>
+          <t xml:space="preserve">23d2b83e16704a7a</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -2376,12 +2376,12 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c969a0b0a8b44d44</t>
+          <t xml:space="preserve">65c2a38708614428</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -2449,12 +2449,12 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a275d4d2bdbd43a5</t>
+          <t xml:space="preserve">c5f237aeac1d4dc5</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -2522,12 +2522,12 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">81076d7b42b1453b</t>
+          <t xml:space="preserve">ce05cbd289a9496a</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">df02842d7d754b1a</t>
+          <t xml:space="preserve">953ae075ea094c7d</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -2668,12 +2668,12 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0af73581267e4f17</t>
+          <t xml:space="preserve">334622b1788047dd</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -2741,12 +2741,12 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fcb856127a66439c</t>
+          <t xml:space="preserve">4b0abd2ffc144338</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2814,12 +2814,12 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bf75bebbfee549ea</t>
+          <t xml:space="preserve">687c79f69abf45bb</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cbc0a08f6fd5430e</t>
+          <t xml:space="preserve">f1c314c5ff644d85</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -2960,12 +2960,12 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fa0442aa15b5412f</t>
+          <t xml:space="preserve">bd4c48d803ad4c9d</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -3033,12 +3033,12 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">75c0a25dbf1747a1</t>
+          <t xml:space="preserve">37219100895f49f3</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -3106,12 +3106,12 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a0194c7b3a1644aa</t>
+          <t xml:space="preserve">554e263697aa4b64</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -3179,12 +3179,12 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ebd90e7b9dc841a9</t>
+          <t xml:space="preserve">294e4828d0044034</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">40724cd57bf74320</t>
+          <t xml:space="preserve">6386970383cb4b6b</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -3325,12 +3325,12 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">03c5312bb42e4dd5</t>
+          <t xml:space="preserve">305740740b814961</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -3398,12 +3398,12 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">14aadf55b6784d6f</t>
+          <t xml:space="preserve">ddfaa688d7454083</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -3471,12 +3471,12 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">be4dc63f296f40ff</t>
+          <t xml:space="preserve">37fdc03ff6484a4b</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -3544,12 +3544,12 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f798c5e41c9f4a5a</t>
+          <t xml:space="preserve">8ada7fd901474e9b</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -3617,12 +3617,12 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">97b3488f01394e35</t>
+          <t xml:space="preserve">45c4fe52ec374976</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -3690,12 +3690,12 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9201efd609ac4c8e</t>
+          <t xml:space="preserve">680b2f02cb5c415d</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -3763,12 +3763,12 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0777ca59e7e942c6</t>
+          <t xml:space="preserve">3427ce33ee90443e</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -3836,12 +3836,12 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">03d231498572440f</t>
+          <t xml:space="preserve">bbd78b9dd9634721</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -3909,12 +3909,12 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b0cf13af88c24f19</t>
+          <t xml:space="preserve">2223227e51a14ae3</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -3982,12 +3982,12 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0cbdd77c57574875</t>
+          <t xml:space="preserve">4bb9ce5302684806</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -4055,12 +4055,12 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7b11a3796f0e498a</t>
+          <t xml:space="preserve">e0c46708162346ed</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -4128,12 +4128,12 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">46e7fbc2e41746e4</t>
+          <t xml:space="preserve">f5db57be17cb456b</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -4201,12 +4201,12 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5175ae14f9c84c13</t>
+          <t xml:space="preserve">4e4f2139ec0b4f0d</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -4274,12 +4274,12 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d3d2da8c4bb6414a</t>
+          <t xml:space="preserve">8e9c17bea02f404f</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -4347,12 +4347,12 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c9048137a2114a0e</t>
+          <t xml:space="preserve">e2301744db4441b1</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -4420,12 +4420,12 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ea7e6fe5faa846ca</t>
+          <t xml:space="preserve">606a6ad72c914566</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -4493,12 +4493,12 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9d72f5c84dcc4f31</t>
+          <t xml:space="preserve">39cff8e0dfb042bf</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -4566,12 +4566,12 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f5d106402da045c2</t>
+          <t xml:space="preserve">acf0e564448248a3</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ce1d6723406146da</t>
+          <t xml:space="preserve">6c5d97c4f0b44353</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -4712,12 +4712,12 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bbc5a11af48d4adc</t>
+          <t xml:space="preserve">3060f4ade2034ba7</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -4785,12 +4785,12 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">30a8a8db88b54a96</t>
+          <t xml:space="preserve">8ae4eeef7a0d426d</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -4858,12 +4858,12 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b169d3e9835949cb</t>
+          <t xml:space="preserve">87ef853120c04fd5</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -4931,12 +4931,12 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">238be9b860c74044</t>
+          <t xml:space="preserve">98a5174e105d4494</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -5004,12 +5004,12 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cf25de2635ca45fe</t>
+          <t xml:space="preserve">dfe4572ff9fb4135</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -5077,12 +5077,12 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">41c38a9f74544f3d</t>
+          <t xml:space="preserve">25e20c861a0445e6</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -5150,12 +5150,12 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e776f73d435046f3</t>
+          <t xml:space="preserve">aa9922f958e246ea</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -5223,12 +5223,12 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">47c4cc5aa6a14202</t>
+          <t xml:space="preserve">7b76cffb5e1c4de3</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -5296,12 +5296,12 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">693195e2a76b4f66</t>
+          <t xml:space="preserve">96ea978d50e34088</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -5369,12 +5369,12 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f1c69bbc76be4106</t>
+          <t xml:space="preserve">ac9f80af0506483c</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -5442,12 +5442,12 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9e06fcfb7d484c3f</t>
+          <t xml:space="preserve">9dba79b271614de2</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -5515,12 +5515,12 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cd8199b7e1aa4e2c</t>
+          <t xml:space="preserve">69499e02f4c84023</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -5588,12 +5588,12 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492d42fcd214407</t>
+          <t xml:space="preserve">1f21043edfd7474e</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -5661,12 +5661,12 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cb32b16d2ab9448e</t>
+          <t xml:space="preserve">d050e9c81f734ce1</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -5734,12 +5734,12 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e93c3c95db1041f0</t>
+          <t xml:space="preserve">db770bd46963440f</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -5807,12 +5807,12 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2b98af99f409415e</t>
+          <t xml:space="preserve">3e13bfb4220a4a3a</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -5880,12 +5880,12 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b1bcce8188264e32</t>
+          <t xml:space="preserve">cc51b1031a884aca</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -5953,12 +5953,12 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e3f244d173ed4ab3</t>
+          <t xml:space="preserve">70d175bc3b424331</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -6026,12 +6026,12 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c006ef0f16ca4e75</t>
+          <t xml:space="preserve">a74483c6f5f8441d</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -6099,12 +6099,12 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">93a2147d16dc475b</t>
+          <t xml:space="preserve">3438f3f240304cde</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -6172,12 +6172,12 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">cf4f000088fa4839</t>
+          <t xml:space="preserve">3bd4a531239c4809</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -6245,12 +6245,12 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">49976e572dc34ec8</t>
+          <t xml:space="preserve">948a8be5bfe14fe2</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -6318,12 +6318,12 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f6346f2c5c8b48ec</t>
+          <t xml:space="preserve">56f4130bad894f67</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -6391,12 +6391,12 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">737b265971064320</t>
+          <t xml:space="preserve">f85389df377e49c6</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -6464,12 +6464,12 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2ba8fa10d1474ee0</t>
+          <t xml:space="preserve">fe64f3e464904f7f</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -6537,12 +6537,12 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7b43152606694c15</t>
+          <t xml:space="preserve">2b3732f50d964b56</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -6610,12 +6610,12 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9163df46664f4fa8</t>
+          <t xml:space="preserve">19478db67f6d4d43</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -6683,12 +6683,12 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5eb2833297d24452</t>
+          <t xml:space="preserve">81efe4a0704f4cda</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -6756,12 +6756,12 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">19db7d23ce494e9f</t>
+          <t xml:space="preserve">7f910006b1cd4c30</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -6829,12 +6829,12 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">701c21df64774e72</t>
+          <t xml:space="preserve">1f498360c55c46a6</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -6902,12 +6902,12 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7daecf8aa1774ca4</t>
+          <t xml:space="preserve">e66dd812e3364da5</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -6975,12 +6975,12 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1adbe66642114c1c</t>
+          <t xml:space="preserve">d473a06d609c4894</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -7048,12 +7048,12 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a44bc8a3ce7b43c7</t>
+          <t xml:space="preserve">c08a40123b7f4679</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -7121,12 +7121,12 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4acbe3f86c06435e</t>
+          <t xml:space="preserve">7340484d15e14520</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">528989b8afb84f70</t>
+          <t xml:space="preserve">b8afc77545464646</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
